--- a/Result/profitability/2450.xlsx
+++ b/Result/profitability/2450.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.32</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5325</v>
+        <v>0.53125</v>
       </c>
       <c r="N2" t="n">
-        <v>10.86125</v>
+        <v>10.77875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.61</v>
+        <v>0.595</v>
       </c>
       <c r="N3" t="n">
-        <v>11.5175</v>
+        <v>11.48125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>0.71125</v>
+        <v>0.7075</v>
       </c>
       <c r="N4" t="n">
-        <v>12.2575</v>
+        <v>12.19875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.88</v>
       </c>
       <c r="M5" t="n">
-        <v>0.765</v>
+        <v>0.7775</v>
       </c>
       <c r="N5" t="n">
-        <v>13.24125</v>
+        <v>13.11875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.14</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8675</v>
+        <v>0.88375</v>
       </c>
       <c r="N6" t="n">
-        <v>14.0075</v>
+        <v>13.95375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.97</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9525</v>
+        <v>0.9225</v>
       </c>
       <c r="N7" t="n">
-        <v>15.31125</v>
+        <v>15.355</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.24</v>
       </c>
       <c r="M8" t="n">
-        <v>1.025</v>
+        <v>1.04625</v>
       </c>
       <c r="N8" t="n">
-        <v>16.4875</v>
+        <v>16.54625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2450</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>8522</v>
+      </c>
+      <c r="D75" t="n">
+        <v>7658</v>
+      </c>
+      <c r="E75" t="n">
+        <v>864</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="G75" t="n">
+        <v>92</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.08%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>35</v>
+      </c>
+      <c r="J75" t="n">
+        <v>127</v>
+      </c>
+      <c r="K75" t="n">
+        <v>108</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.39125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6799999999999999</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.4700000000000006</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.04860392967942095</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.9799999999999986</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.08812949640287759</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
